--- a/evaluation/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/NL2SPARQL_Evaluation_Results.xlsx
@@ -1673,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>42.52</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="3">
@@ -1734,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>17.01</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="4">
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>17.47</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="5">
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>21.1</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="6">
@@ -1917,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>19.05</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="7">
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>19.54</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="8">
@@ -2039,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>17.63</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="9">
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>17.65</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="10">
@@ -2161,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>18.36</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="11">
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>21.45</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="12">
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>17.1</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="13">
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>18.06</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="14">
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>32.6</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="15">
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>29.87</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="16">
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>30.33</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="17">
@@ -2566,18 +2566,18 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L17" s="5" t="n"/>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>35.8</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="18">
@@ -2627,18 +2627,18 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I18" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L18" s="5" t="n"/>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>14.28</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="19">
@@ -2688,18 +2688,18 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L19" s="5" t="n"/>
@@ -2707,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>14.2</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="20">
@@ -2771,7 +2771,7 @@
         <v>0.4</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>26.99</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="21">
@@ -2832,7 +2832,7 @@
         <v>0.4</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>21.63</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="22">
@@ -2893,7 +2893,7 @@
         <v>0.4</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>22.4</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="23">
@@ -2954,7 +2954,7 @@
         <v>0.4</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>23.4</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="24">
@@ -3015,7 +3015,7 @@
         <v>0.4</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>24.55</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="25">
@@ -3076,7 +3076,7 @@
         <v>0.4</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>25.33</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="26">
@@ -3137,7 +3137,7 @@
         <v>0.4</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>24.93</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="27">
@@ -3198,7 +3198,7 @@
         <v>0.4</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>23.96</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="28">
@@ -3259,7 +3259,7 @@
         <v>0.4</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>24.58</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="29">
@@ -3320,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>17.93</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="30">
@@ -3381,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>15.81</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="31">
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>16.28</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="32">
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>17.32</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="33">
@@ -3564,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>15.35</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="34">
@@ -3625,7 +3625,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>16.04</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="35">
@@ -3686,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>20.32</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="36">
@@ -3747,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>18.95</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="37">
@@ -3808,7 +3808,7 @@
         <v>1</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>19.71</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="38">
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>27.71</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="39">
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>22.06</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="40">
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>23.3</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="41">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>25.56</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="42">
@@ -4113,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>26.87</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="43">
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>27.35</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="44">
@@ -4235,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>26.67</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="45">
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>28.89</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="46">
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>27.82</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="47">
@@ -4418,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>23.28</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="48">
@@ -4479,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>17.37</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="49">
@@ -4540,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>18.45</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="50">
@@ -4601,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>26.54</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="51">
@@ -4662,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>19.78</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="52">
@@ -4723,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>21.19</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="53">
@@ -4762,29 +4762,29 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I53" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>7.82</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="54">
@@ -4823,29 +4823,29 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I54" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>7.32</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="55">
@@ -4884,29 +4884,29 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I55" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>7.7</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="56">
@@ -4967,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>21.17</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="57">
@@ -5028,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>15.9</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="58">
@@ -5089,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>17.34</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="59">
@@ -5150,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>24.58</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="60">
@@ -5211,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>20.4</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="61">
@@ -5272,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>20.38</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="62">
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>17.01</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="63">
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>11.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="64">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>12.3</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="65">
@@ -5516,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>13.16</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="66">
@@ -5577,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>12.26</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="67">
@@ -5638,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>12.57</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="68">
@@ -5699,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>15.63</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5760,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>16.35</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="70">
@@ -5821,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>15.25</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="71">
@@ -5882,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>20.5</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="72">
@@ -5943,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>15.49</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="73">
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>15.56</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="74">
@@ -6065,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>20.7</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="75">
@@ -6126,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>17.16</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="76">
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>17.55</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="77">
@@ -6226,14 +6226,14 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I77" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>11.7</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="78">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I78" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>8</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="79">
@@ -6348,14 +6348,14 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I79" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>7.81</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="80">
@@ -6416,22 +6416,22 @@
         <v>1</v>
       </c>
       <c r="J80" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>5.07</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="81">
@@ -6477,22 +6477,22 @@
         <v>1</v>
       </c>
       <c r="J81" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>4.83</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="82">
@@ -6538,22 +6538,22 @@
         <v>1</v>
       </c>
       <c r="J82" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>5.25</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="83">
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>14.3</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="84">
@@ -6675,7 +6675,7 @@
         <v>1</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>12.66</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>13.3</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="86">
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>14.48</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="87">
@@ -6858,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>13.35</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="88">
@@ -6919,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>13.48</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="89">
@@ -6980,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>15.9</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="90">
@@ -7041,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>14.14</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="91">
@@ -7102,7 +7102,7 @@
         <v>1</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>13.97</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="92">
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>12.89</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="93">
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>11.17</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="94">
@@ -7285,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>11.61</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="95">
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>13.73</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="96">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>11.28</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="97">
@@ -7468,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>11.6</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="98">
@@ -7529,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>13.59</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="99">
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>11.95</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="100">
@@ -7651,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>12.11</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="101">
@@ -7712,7 +7712,7 @@
         <v>1</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>26.72</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="102">
@@ -7773,7 +7773,7 @@
         <v>1</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>17.59</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="103">
@@ -7834,7 +7834,7 @@
         <v>1</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>18.46</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="104">
@@ -7873,29 +7873,29 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I104" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L104" s="5" t="n"/>
       <c r="M104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>11.81</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="105">
@@ -7934,29 +7934,29 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I105" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>6.94</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="106">
@@ -7995,29 +7995,29 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I106" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L106" s="5" t="n"/>
       <c r="M106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>7.58</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="107">
@@ -8078,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>20.03</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="108">
@@ -8139,7 +8139,7 @@
         <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>15.08</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="109">
@@ -8200,7 +8200,7 @@
         <v>1</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>15.73</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="110">
@@ -8261,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>27.29</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="111">
@@ -8322,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>19.01</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="112">
@@ -8383,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>19.17</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="113">
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>23.72</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="114">
@@ -8505,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>19.81</v>
+        <v>16.03</v>
       </c>
     </row>
     <row r="115">
@@ -8566,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>19.85</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="116">
@@ -8627,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>6.84</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="117">
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>4.02</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -8749,7 +8749,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="119">
@@ -8810,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>23.37</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="120">
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>19.38</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="121">
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>19.57</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="122">
@@ -8993,7 +8993,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>23.58</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="123">
@@ -9054,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>19.64</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="124">
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>20.45</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="125">
@@ -9176,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>23.74</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="126">
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="O126" s="5" t="n">
-        <v>19.51</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="127">
@@ -9298,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>19.68</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="128">
@@ -9344,18 +9344,14 @@
         <v>1</v>
       </c>
       <c r="J128" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="n"/>
       <c r="M128" s="5" t="n">
         <v>0</v>
       </c>
@@ -9363,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>10.51</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="129">
@@ -9409,18 +9405,14 @@
         <v>1</v>
       </c>
       <c r="J129" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L129" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="n"/>
       <c r="M129" s="5" t="n">
         <v>0</v>
       </c>
@@ -9428,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="O129" s="5" t="n">
-        <v>6.45</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="130">
@@ -9474,18 +9466,14 @@
         <v>1</v>
       </c>
       <c r="J130" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="n"/>
       <c r="M130" s="5" t="n">
         <v>0</v>
       </c>
@@ -9493,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="O130" s="5" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="131">
@@ -9539,18 +9527,14 @@
         <v>1</v>
       </c>
       <c r="J131" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="n"/>
       <c r="M131" s="5" t="n">
         <v>0</v>
       </c>
@@ -9558,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="5" t="n">
-        <v>9.720000000000001</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="132">
@@ -9604,18 +9588,14 @@
         <v>1</v>
       </c>
       <c r="J132" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="n"/>
       <c r="M132" s="5" t="n">
         <v>0</v>
       </c>
@@ -9623,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>6.39</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -9669,18 +9649,14 @@
         <v>1</v>
       </c>
       <c r="J133" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n">
         <v>0</v>
       </c>
@@ -9688,7 +9664,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="5" t="n">
-        <v>6.46</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="134">
@@ -9734,18 +9710,14 @@
         <v>1</v>
       </c>
       <c r="J134" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n">
         <v>0</v>
       </c>
@@ -9753,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="5" t="n">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="135">
@@ -9799,18 +9771,14 @@
         <v>1</v>
       </c>
       <c r="J135" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L135" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="n"/>
       <c r="M135" s="5" t="n">
         <v>0</v>
       </c>
@@ -9818,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="5" t="n">
-        <v>27.87</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="136">
@@ -9864,18 +9832,14 @@
         <v>1</v>
       </c>
       <c r="J136" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
-          <t>sparql_build_failure</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>params={'property': 'country', 'mode': 'count'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="n"/>
       <c r="M136" s="5" t="n">
         <v>0</v>
       </c>
@@ -9883,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="5" t="n">
-        <v>27.96</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="137">
@@ -9944,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>45.45</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="138">
@@ -10005,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>40.74</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -10066,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="5" t="n">
-        <v>41.72</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="140">
@@ -10105,11 +10069,11 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I140" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" s="5" t="b">
         <v>1</v>
@@ -10127,7 +10091,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>66.76000000000001</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="141">
@@ -10166,11 +10130,11 @@
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I141" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" s="5" t="b">
         <v>1</v>
@@ -10188,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>22.55</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="142">
@@ -10227,11 +10191,11 @@
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I142" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" s="5" t="b">
         <v>1</v>
@@ -10249,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>12.38</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="143">
@@ -10310,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="5" t="n">
-        <v>12.7</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="144">
@@ -10371,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>9.5</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="145">
@@ -10432,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="5" t="n">
-        <v>9.49</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="146">
@@ -10478,22 +10442,26 @@
         <v>1</v>
       </c>
       <c r="J146" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L146" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
+        </is>
+      </c>
       <c r="M146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" s="5" t="n">
-        <v>13.91</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="147">
@@ -10539,22 +10507,26 @@
         <v>1</v>
       </c>
       <c r="J147" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L147" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
+        </is>
+      </c>
       <c r="M147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147" s="5" t="n">
-        <v>9.9</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="148">
@@ -10600,22 +10572,26 @@
         <v>1</v>
       </c>
       <c r="J148" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="L148" s="5" t="n"/>
+          <t>sparql_build_failure</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
+        </is>
+      </c>
       <c r="M148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>10.07</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -10665,12 +10641,12 @@
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>params={'airport1': 'all', 'airport2': 'null', 'property': 'elevationFt'}</t>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
         </is>
       </c>
       <c r="M149" s="5" t="n">
@@ -10680,7 +10656,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="5" t="n">
-        <v>14.1</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="150">
@@ -10730,12 +10706,12 @@
       </c>
       <c r="K150" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>params={'airport1': 'all', 'airport2': 'null', 'property': 'elevationFt'}</t>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
         </is>
       </c>
       <c r="M150" s="5" t="n">
@@ -10745,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="5" t="n">
-        <v>10.68</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="151">
@@ -10795,12 +10771,12 @@
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
+          <t>sparql_build_failure</t>
         </is>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>params={'airport1': 'all', 'airport2': 'null', 'property': 'elevationFt'}</t>
+          <t>params={'group_by': 'airport', 'property': 'elevationFt', 'function': 'MAX', 'limit': 1}</t>
         </is>
       </c>
       <c r="M151" s="5" t="n">
@@ -10810,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="5" t="n">
-        <v>10.56</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="152">
@@ -10856,18 +10832,14 @@
         <v>1</v>
       </c>
       <c r="J152" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L152" s="5" t="inlineStr">
-        <is>
-          <t>params={'airport1': '???', 'airport2': '???', 'property': 'elevationFt'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="n"/>
       <c r="M152" s="5" t="n">
         <v>0</v>
       </c>
@@ -10875,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="5" t="n">
-        <v>11.5</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="153">
@@ -10921,26 +10893,22 @@
         <v>1</v>
       </c>
       <c r="J153" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L153" s="5" t="inlineStr">
-        <is>
-          <t>params={'airport1': '???', 'airport2': '???', 'property': 'elevationFt'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="n"/>
       <c r="M153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" s="5" t="n">
-        <v>8.99</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="154">
@@ -10986,26 +10954,22 @@
         <v>1</v>
       </c>
       <c r="J154" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>execution_failure</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr">
-        <is>
-          <t>params={'airport1': '???', 'airport2': '???', 'property': 'elevationFt'}</t>
-        </is>
-      </c>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="n"/>
       <c r="M154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" s="5" t="n">
-        <v>9.01</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="155">
@@ -11066,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="5" t="n">
-        <v>7.62</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="156">
@@ -11127,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="O156" s="5" t="n">
-        <v>5.15</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="157">
@@ -11166,11 +11130,11 @@
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I157" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" s="5" t="b">
         <v>1</v>
@@ -11182,13 +11146,13 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" s="5" t="n">
-        <v>10.26</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="158">
@@ -11249,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="5" t="n">
-        <v>36.18</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="159">
@@ -11310,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="5" t="n">
-        <v>26.82</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="160">
@@ -11371,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="5" t="n">
-        <v>26.38</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="161">
@@ -11436,7 +11400,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="5" t="n">
-        <v>8</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="162">
@@ -11501,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="5" t="n">
-        <v>7.95</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="163">
@@ -11566,7 +11530,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="5" t="n">
-        <v>8</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="164">
@@ -11631,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="5" t="n">
-        <v>11.17</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="165">
@@ -11696,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="5" t="n">
-        <v>7.95</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="166">
@@ -11761,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="5" t="n">
-        <v>8.01</v>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/NL2SPARQL_Evaluation_Results.xlsx
+++ b/evaluation/NL2SPARQL_Evaluation_Results.xlsx
@@ -1673,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>25.51</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="3">
@@ -1734,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>13.55</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="4">
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>13.96</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="5">
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>15.56</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="6">
@@ -1917,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>15.78</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="7">
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>16.23</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="8">
@@ -2039,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>16.39</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="9">
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>15.46</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="10">
@@ -2161,13 +2161,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>16.03</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -2222,13 +2222,13 @@
         <v>1</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>15.79</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -2283,13 +2283,13 @@
         <v>1</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>14.23</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -2344,13 +2344,13 @@
         <v>1</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>14.9</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -2399,19 +2399,19 @@
       </c>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>16.11</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -2460,19 +2460,19 @@
       </c>
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>14.19</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -2521,19 +2521,19 @@
       </c>
       <c r="L16" s="5" t="n"/>
       <c r="M16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>14.37</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -2588,13 +2588,13 @@
         <v>1</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>16.7</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -2649,13 +2649,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>16.47</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_013</t>
+          <t>single_kg1_011</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -2710,13 +2710,13 @@
         <v>1</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>18.34</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I20" s="5" t="b">
@@ -2771,13 +2771,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>15.3</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I21" s="5" t="b">
@@ -2832,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>13.22</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I22" s="5" t="b">
@@ -2893,13 +2893,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>13.31</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I23" s="5" t="b">
@@ -2954,13 +2954,13 @@
         <v>1</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>19.2</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I24" s="5" t="b">
@@ -3015,13 +3015,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>15.24</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I25" s="5" t="b">
@@ -3076,13 +3076,13 @@
         <v>1</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>15.96</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I26" s="5" t="b">
@@ -3137,13 +3137,13 @@
         <v>1</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>15.81</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I27" s="5" t="b">
@@ -3198,13 +3198,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>14.42</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_011</t>
+          <t>single_kg1_012</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I28" s="5" t="b">
@@ -3259,13 +3259,13 @@
         <v>1</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>15.43</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I29" s="5" t="b">
@@ -3320,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>17.06</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I30" s="5" t="b">
@@ -3381,13 +3381,13 @@
         <v>1</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>13.48</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I31" s="5" t="b">
@@ -3442,13 +3442,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>13.96</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I32" s="5" t="b">
@@ -3503,13 +3503,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>18.3</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I33" s="5" t="b">
@@ -3564,13 +3564,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>16.08</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I34" s="5" t="b">
@@ -3625,13 +3625,13 @@
         <v>1</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>16.72</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I35" s="5" t="b">
@@ -3686,13 +3686,13 @@
         <v>1</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>14.37</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I36" s="5" t="b">
@@ -3747,13 +3747,13 @@
         <v>1</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>15.57</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_012</t>
+          <t>single_kg1_013</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>flights</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>single_kg1</t>
         </is>
       </c>
       <c r="I37" s="5" t="b">
@@ -3808,13 +3808,13 @@
         <v>1</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>16.38</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I38" s="5" t="b">
@@ -3869,13 +3869,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>10.15</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I39" s="5" t="b">
@@ -3930,13 +3930,13 @@
         <v>1</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>10.98</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I40" s="5" t="b">
@@ -3991,13 +3991,13 @@
         <v>1</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>10.81</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I41" s="5" t="b">
@@ -4052,13 +4052,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>10.36</v>
+        <v>35.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I42" s="5" t="b">
@@ -4113,13 +4113,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>11.98</v>
+        <v>25.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I43" s="5" t="b">
@@ -4174,13 +4174,13 @@
         <v>1</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>12.23</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I44" s="5" t="b">
@@ -4235,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>11.15</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I45" s="5" t="b">
@@ -4296,13 +4296,13 @@
         <v>1</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>11.9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_005</t>
+          <t>single_kg2_010</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I46" s="5" t="b">
@@ -4357,13 +4357,13 @@
         <v>1</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>12.59</v>
+        <v>24.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I47" s="5" t="b">
@@ -4418,13 +4418,13 @@
         <v>1</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>14.42</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I48" s="5" t="b">
@@ -4479,13 +4479,13 @@
         <v>1</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>11.44</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I49" s="5" t="b">
@@ -4540,13 +4540,13 @@
         <v>1</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>11.79</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I50" s="5" t="b">
@@ -4601,13 +4601,13 @@
         <v>1</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>11.41</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I51" s="5" t="b">
@@ -4662,13 +4662,13 @@
         <v>1</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>12.61</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I52" s="5" t="b">
@@ -4723,13 +4723,13 @@
         <v>1</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>12.74</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -4757,40 +4757,40 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L53" s="5" t="n"/>
       <c r="M53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>12.23</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4818,40 +4818,40 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I54" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L54" s="5" t="n"/>
       <c r="M54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>13.67</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_006</t>
+          <t>single_kg2_011</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -4879,40 +4879,40 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I55" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>13.73</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I56" s="5" t="b">
@@ -4967,13 +4967,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>12.1</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I57" s="5" t="b">
@@ -5028,13 +5028,13 @@
         <v>1</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>10.19</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I58" s="5" t="b">
@@ -5089,13 +5089,13 @@
         <v>1</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>10.49</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I59" s="5" t="b">
@@ -5150,13 +5150,13 @@
         <v>1</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>12.05</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I60" s="5" t="b">
@@ -5211,13 +5211,13 @@
         <v>1</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>11.48</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I61" s="5" t="b">
@@ -5272,13 +5272,13 @@
         <v>1</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>11.82</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I62" s="5" t="b">
@@ -5333,13 +5333,13 @@
         <v>1</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>13.75</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I63" s="5" t="b">
@@ -5394,13 +5394,13 @@
         <v>1</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>12.36</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_007</t>
+          <t>single_kg2_012</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>single_kg2</t>
         </is>
       </c>
       <c r="I64" s="5" t="b">
@@ -5455,13 +5455,13 @@
         <v>1</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>12.51</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I65" s="5" t="b">
@@ -5516,13 +5516,13 @@
         <v>1</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>18.86</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I66" s="5" t="b">
@@ -5577,13 +5577,13 @@
         <v>1</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>14.12</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I67" s="5" t="b">
@@ -5638,13 +5638,13 @@
         <v>1</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>14.47</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I68" s="5" t="b">
@@ -5699,13 +5699,13 @@
         <v>1</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>17.66</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I69" s="5" t="b">
@@ -5760,13 +5760,13 @@
         <v>1</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>15.38</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B70" s="5" t="n">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I70" s="5" t="b">
@@ -5821,13 +5821,13 @@
         <v>1</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>16.38</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I71" s="5" t="b">
@@ -5882,13 +5882,13 @@
         <v>1</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>15.66</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I72" s="5" t="b">
@@ -5943,13 +5943,13 @@
         <v>1</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>13.46</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_013</t>
+          <t>single_kg3_005</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I73" s="5" t="b">
@@ -6004,21 +6004,21 @@
         <v>1</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>14</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I74" s="5" t="b">
@@ -6059,27 +6059,27 @@
       </c>
       <c r="L74" s="5" t="n"/>
       <c r="M74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>7.78</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I75" s="5" t="b">
@@ -6120,27 +6120,27 @@
       </c>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>8.41</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I76" s="5" t="b">
@@ -6181,27 +6181,27 @@
       </c>
       <c r="L76" s="5" t="n"/>
       <c r="M76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>8.42</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I77" s="5" t="b">
@@ -6242,27 +6242,27 @@
       </c>
       <c r="L77" s="5" t="n"/>
       <c r="M77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>10.43</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I78" s="5" t="b">
@@ -6303,27 +6303,27 @@
       </c>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>8.619999999999999</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I79" s="5" t="b">
@@ -6364,27 +6364,27 @@
       </c>
       <c r="L79" s="5" t="n"/>
       <c r="M79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>8.56</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I80" s="5" t="b">
@@ -6425,27 +6425,27 @@
       </c>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>7.88</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -6465,12 +6465,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I81" s="5" t="b">
@@ -6486,27 +6486,27 @@
       </c>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>9.039999999999999</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3_003</t>
+          <t>single_kg3_006</t>
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>filter_string_kg3</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I82" s="5" t="b">
@@ -6547,32 +6547,32 @@
       </c>
       <c r="L82" s="5" t="n"/>
       <c r="M82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I83" s="5" t="b">
@@ -6614,26 +6614,26 @@
         <v>1</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>22.64</v>
+        <v>11.79</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I84" s="5" t="b">
@@ -6675,26 +6675,26 @@
         <v>1</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I85" s="5" t="b">
@@ -6736,26 +6736,26 @@
         <v>1</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>8.27</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I86" s="5" t="b">
@@ -6797,26 +6797,26 @@
         <v>1</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>12.5</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I87" s="5" t="b">
@@ -6858,26 +6858,26 @@
         <v>1</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>9.81</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B88" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I88" s="5" t="b">
@@ -6919,26 +6919,26 @@
         <v>1</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>9.74</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I89" s="5" t="b">
@@ -6974,32 +6974,32 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>10.55</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B90" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I90" s="5" t="b">
@@ -7035,32 +7035,32 @@
       </c>
       <c r="L90" s="5" t="n"/>
       <c r="M90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>8.970000000000001</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2_004</t>
+          <t>single_kg3_007</t>
         </is>
       </c>
       <c r="B91" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>ranking_kg2</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I91" s="5" t="b">
@@ -7096,19 +7096,19 @@
       </c>
       <c r="L91" s="5" t="n"/>
       <c r="M91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B92" s="5" t="n">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I92" s="5" t="b">
@@ -7157,19 +7157,19 @@
       </c>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>31.97</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B93" s="5" t="n">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I93" s="5" t="b">
@@ -7218,19 +7218,19 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>13.13</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I94" s="5" t="b">
@@ -7279,19 +7279,19 @@
       </c>
       <c r="L94" s="5" t="n"/>
       <c r="M94" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>13.11</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I95" s="5" t="b">
@@ -7340,19 +7340,19 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>20.48</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I96" s="5" t="b">
@@ -7401,19 +7401,19 @@
       </c>
       <c r="L96" s="5" t="n"/>
       <c r="M96" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>15.68</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I97" s="5" t="b">
@@ -7462,19 +7462,19 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>15.67</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -7502,19 +7502,19 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I98" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7526,16 +7526,16 @@
         <v>0</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>9.640000000000001</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B99" s="5" t="n">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -7563,19 +7563,19 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I99" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7587,16 +7587,16 @@
         <v>0</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>6.06</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>open_kg_007</t>
+          <t>single_kg3_008</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -7624,19 +7624,19 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>open_kg</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>out_of_scope</t>
+          <t>single_kg3</t>
         </is>
       </c>
       <c r="I100" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
@@ -7648,16 +7648,16 @@
         <v>0</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>7.06</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I101" s="5" t="b">
@@ -7706,19 +7706,19 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>17.67</v>
+        <v>23.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I102" s="5" t="b">
@@ -7767,19 +7767,19 @@
       </c>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>15.74</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I103" s="5" t="b">
@@ -7828,19 +7828,19 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>16.67</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -7868,23 +7868,23 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I104" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L104" s="5" t="n"/>
@@ -7892,16 +7892,16 @@
         <v>0</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>18.23</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B105" s="5" t="n">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -7929,23 +7929,23 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I105" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L105" s="5" t="n"/>
@@ -7953,16 +7953,16 @@
         <v>0</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>17.31</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -7990,23 +7990,23 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I106" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>mapping_failure</t>
         </is>
       </c>
       <c r="L106" s="5" t="n"/>
@@ -8014,16 +8014,16 @@
         <v>0</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>19.3</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I107" s="5" t="b">
@@ -8072,19 +8072,19 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>18.7</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I108" s="5" t="b">
@@ -8139,13 +8139,13 @@
         <v>1</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>18.98</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_011</t>
+          <t>cross_kg_013</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I109" s="5" t="b">
@@ -8200,13 +8200,13 @@
         <v>1</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>19.71</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B110" s="5" t="n">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I110" s="5" t="b">
@@ -8261,13 +8261,13 @@
         <v>1</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>22.26</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I111" s="5" t="b">
@@ -8322,13 +8322,13 @@
         <v>1</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>20.17</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I112" s="5" t="b">
@@ -8383,13 +8383,13 @@
         <v>1</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>21.27</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I113" s="5" t="b">
@@ -8444,13 +8444,13 @@
         <v>1</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>21.32</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B114" s="5" t="n">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I114" s="5" t="b">
@@ -8505,13 +8505,13 @@
         <v>1</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>22.1</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I115" s="5" t="b">
@@ -8566,13 +8566,13 @@
         <v>1</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>22.7</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I116" s="5" t="b">
@@ -8627,13 +8627,13 @@
         <v>1</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>21.41</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I117" s="5" t="b">
@@ -8688,13 +8688,13 @@
         <v>1</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>21.08</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>single_kg1_012</t>
+          <t>cross_kg_014</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I118" s="5" t="b">
@@ -8749,13 +8749,13 @@
         <v>1</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>21.46</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I119" s="5" t="b">
@@ -8810,13 +8810,13 @@
         <v>1</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>23.13</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I120" s="5" t="b">
@@ -8871,13 +8871,13 @@
         <v>1</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>19.15</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I121" s="5" t="b">
@@ -8932,13 +8932,13 @@
         <v>1</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>21.03</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I122" s="5" t="b">
@@ -8993,13 +8993,13 @@
         <v>1</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>33.41</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I123" s="5" t="b">
@@ -9054,13 +9054,13 @@
         <v>1</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>23.75</v>
+        <v>18.85</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I124" s="5" t="b">
@@ -9115,13 +9115,13 @@
         <v>1</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>23.89</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I125" s="5" t="b">
@@ -9176,13 +9176,13 @@
         <v>1</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>21.83</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I126" s="5" t="b">
@@ -9237,13 +9237,13 @@
         <v>1</v>
       </c>
       <c r="O126" s="5" t="n">
-        <v>22.82</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>single_kg2_010</t>
+          <t>cross_kg_015</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>cross_kg</t>
         </is>
       </c>
       <c r="I127" s="5" t="b">
@@ -9298,26 +9298,26 @@
         <v>1</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>23.17</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I128" s="5" t="b">
@@ -9353,32 +9353,32 @@
       </c>
       <c r="L128" s="5" t="n"/>
       <c r="M128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>11.98</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I129" s="5" t="b">
@@ -9414,32 +9414,32 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O129" s="5" t="n">
-        <v>9.82</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -9454,12 +9454,12 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I130" s="5" t="b">
@@ -9475,32 +9475,32 @@
       </c>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O130" s="5" t="n">
-        <v>10.12</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I131" s="5" t="b">
@@ -9536,32 +9536,32 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O131" s="5" t="n">
-        <v>11.97</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I132" s="5" t="b">
@@ -9597,32 +9597,32 @@
       </c>
       <c r="L132" s="5" t="n"/>
       <c r="M132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>11.36</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I133" s="5" t="b">
@@ -9658,32 +9658,32 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O133" s="5" t="n">
-        <v>12.3</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B134" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I134" s="5" t="b">
@@ -9719,32 +9719,32 @@
       </c>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O134" s="5" t="n">
-        <v>12.52</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I135" s="5" t="b">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O135" s="5" t="n">
-        <v>11.62</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>single_kg3_008</t>
+          <t>group_agg_kg2_001</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>group_aggregate_kg2</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>single_kg3</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I136" s="5" t="b">
@@ -9841,32 +9841,32 @@
       </c>
       <c r="L136" s="5" t="n"/>
       <c r="M136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O136" s="5" t="n">
-        <v>11.75</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I137" s="5" t="b">
@@ -9902,32 +9902,32 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>17.84</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I138" s="5" t="b">
@@ -9963,32 +9963,32 @@
       </c>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>16.02</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I139" s="5" t="b">
@@ -10024,32 +10024,32 @@
       </c>
       <c r="L139" s="5" t="n"/>
       <c r="M139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" s="5" t="n">
-        <v>16.15</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I140" s="5" t="b">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>18.65</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I141" s="5" t="b">
@@ -10146,32 +10146,32 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>16.27</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I142" s="5" t="b">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="L142" s="5" t="n"/>
       <c r="M142" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>16.82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -10247,23 +10247,23 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I143" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L143" s="5" t="n"/>
@@ -10274,26 +10274,26 @@
         <v>0</v>
       </c>
       <c r="O143" s="5" t="n">
-        <v>4.68</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B144" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -10308,23 +10308,23 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I144" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L144" s="5" t="n"/>
@@ -10335,26 +10335,26 @@
         <v>0</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>2.1</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_014</t>
+          <t>filter_string_kg3_003</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>filter_string_kg3</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -10369,23 +10369,23 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>single_kg1</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I145" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
-          <t>mapping_failure</t>
+          <t>success</t>
         </is>
       </c>
       <c r="L145" s="5" t="n"/>
@@ -10396,26 +10396,26 @@
         <v>0</v>
       </c>
       <c r="O145" s="5" t="n">
-        <v>2.43</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -10430,12 +10430,12 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I146" s="5" t="b">
@@ -10457,26 +10457,26 @@
         <v>1</v>
       </c>
       <c r="O146" s="5" t="n">
-        <v>16.55</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -10491,12 +10491,12 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I147" s="5" t="b">
@@ -10518,26 +10518,26 @@
         <v>1</v>
       </c>
       <c r="O147" s="5" t="n">
-        <v>15.41</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I148" s="5" t="b">
@@ -10579,26 +10579,26 @@
         <v>1</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>16.04</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I149" s="5" t="b">
@@ -10640,26 +10640,26 @@
         <v>1</v>
       </c>
       <c r="O149" s="5" t="n">
-        <v>18.59</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I150" s="5" t="b">
@@ -10701,26 +10701,26 @@
         <v>1</v>
       </c>
       <c r="O150" s="5" t="n">
-        <v>16.32</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -10735,12 +10735,12 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I151" s="5" t="b">
@@ -10762,26 +10762,26 @@
         <v>1</v>
       </c>
       <c r="O151" s="5" t="n">
-        <v>16.81</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I152" s="5" t="b">
@@ -10823,26 +10823,26 @@
         <v>1</v>
       </c>
       <c r="O152" s="5" t="n">
-        <v>18.71</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I153" s="5" t="b">
@@ -10884,26 +10884,26 @@
         <v>1</v>
       </c>
       <c r="O153" s="5" t="n">
-        <v>16.57</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>cross_kg_015</t>
+          <t>ranking_kg2_004</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>ranking_kg2</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>airports</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>cross_kg</t>
+          <t>template</t>
         </is>
       </c>
       <c r="I154" s="5" t="b">
@@ -10945,26 +10945,26 @@
         <v>1</v>
       </c>
       <c r="O154" s="5" t="n">
-        <v>16.48</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I155" s="5" t="b">
@@ -11006,46 +11006,46 @@
         <v>1</v>
       </c>
       <c r="O155" s="5" t="n">
-        <v>11.37</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>few-shot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I156" s="5" t="b">
@@ -11067,46 +11067,46 @@
         <v>1</v>
       </c>
       <c r="O156" s="5" t="n">
-        <v>8.609999999999999</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>ask_query_005</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>cot</t>
+          <t>zero-shot</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>ask_query</t>
         </is>
       </c>
       <c r="I157" s="5" t="b">
@@ -11122,37 +11122,37 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" s="5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
@@ -11162,12 +11162,12 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I158" s="5" t="b">
@@ -11189,31 +11189,31 @@
         <v>1</v>
       </c>
       <c r="O158" s="5" t="n">
-        <v>11.01</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I159" s="5" t="b">
@@ -11250,31 +11250,31 @@
         <v>1</v>
       </c>
       <c r="O159" s="5" t="n">
-        <v>8.73</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I160" s="5" t="b">
@@ -11311,31 +11311,31 @@
         <v>1</v>
       </c>
       <c r="O160" s="5" t="n">
-        <v>8.65</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I161" s="5" t="b">
@@ -11372,31 +11372,31 @@
         <v>1</v>
       </c>
       <c r="O161" s="5" t="n">
-        <v>10.63</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I162" s="5" t="b">
@@ -11433,31 +11433,31 @@
         <v>1</v>
       </c>
       <c r="O162" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
         <is>
-          <t>group_agg_kg2_001</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>group_aggregate_kg2</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>airports</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>template</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="I163" s="5" t="b">
@@ -11494,31 +11494,31 @@
         <v>1</v>
       </c>
       <c r="O163" s="5" t="n">
-        <v>8.67</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -11528,19 +11528,19 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I164" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" s="5" t="inlineStr">
         <is>
@@ -11549,59 +11549,59 @@
       </c>
       <c r="L164" s="5" t="n"/>
       <c r="M164" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" s="5" t="n">
-        <v>4.67</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>few-shot</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I165" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" s="5" t="inlineStr">
         <is>
@@ -11610,32 +11610,32 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" s="5" t="n">
-        <v>4.64</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>ask_query_005</t>
+          <t>open_kg_007</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>cross</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -11645,24 +11645,24 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>zero-shot</t>
+          <t>cot</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>ask_query</t>
+          <t>open_kg</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>single_kg2</t>
+          <t>out_of_scope</t>
         </is>
       </c>
       <c r="I166" s="5" t="b">
         <v>0</v>
       </c>
       <c r="J166" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" s="5" t="inlineStr">
         <is>
@@ -11671,13 +11671,13 @@
       </c>
       <c r="L166" s="5" t="n"/>
       <c r="M166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O166" s="5" t="n">
-        <v>22.36</v>
+        <v>6.42</v>
       </c>
     </row>
   </sheetData>
